--- a/latest_print_file.xlsx
+++ b/latest_print_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>成分：新疆红枣</t>
+          <t>成分：建宁白莲</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>规格：散装称重</t>
+          <t>规格：去芯</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>净重：500克</t>
+          <t>净重：250克</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,23 +508,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>产地：新疆</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>产地：福建三明建宁县</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6752873dbdb5900001a803f0</t>
+          <t>66865659d042ed000112d491</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>储存方式：密封冰箱保鲜</t>
+          <t>储存方式：密封冰箱冷藏</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>xjhz</t>
+          <t>lz</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -535,17 +539,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>成分：椴木小银耳</t>
+          <t>成分：建宁白莲</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>规格：散装称重</t>
+          <t>规格：去芯</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>净重：100克</t>
+          <t>净重：250克</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -555,17 +559,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>产地：福建宁德古田县</t>
+          <t>产地：福建三明建宁县</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>等级：精选整朵</t>
+          <t> </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>677f52e7fb21c20001a76511</t>
+          <t>66865659d042ed000112d491</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,11 +579,199 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ye</t>
+          <t>lz</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>成分：建宁白莲</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>规格：去芯</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>净重：500克</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>保质期：6个月</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>产地：福建三明建宁县</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>66865659d042ed000112d494</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>储存方式：密封冰箱冷藏</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>lz</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>成分：建宁白莲</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>规格：去芯</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>净重：500克</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>保质期：6个月</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>产地：福建三明建宁县</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>66865659d042ed000112d494</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>储存方式：密封冰箱冷藏</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>lz</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>成分：建宁白莲</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>规格：去芯</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>净重：500克</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>保质期：6个月</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>产地：福建三明建宁县</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>66865659d042ed000112d494</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>储存方式：密封冰箱冷藏</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>lz</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>成分：龙牙百合</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>规格：中芯片</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>净重：250克</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>保质期：6个月</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>产地：湖南隆回</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>67a72cef96b36c000150e9c6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>储存方式：密封冰箱冷藏</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>bh</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
     </row>
